--- a/Result/profitability/2547.xlsx
+++ b/Result/profitability/2547.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4725000000000003</v>
+        <v>0.4762500000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>49.44750000000001</v>
+        <v>49.17875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4287500000000002</v>
+        <v>0.4012500000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>43.55375</v>
+        <v>42.00625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4100000000000003</v>
+        <v>0.04375000000000022</v>
       </c>
       <c r="N4" t="n">
-        <v>43.33375</v>
+        <v>41.0975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08375000000000023</v>
+        <v>0.08125000000000022</v>
       </c>
       <c r="N5" t="n">
-        <v>42.7375</v>
+        <v>41.19625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09125000000000023</v>
+        <v>0.08250000000000023</v>
       </c>
       <c r="N6" t="n">
-        <v>43.7525</v>
+        <v>41.8925</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1962500000000002</v>
+        <v>0.1812500000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>42.18</v>
+        <v>40.795</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.68</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2712500000000002</v>
+        <v>0.2587500000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>41.63125</v>
+        <v>39.92</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.9525000000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>46.93125</v>
+        <v>46.93125000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>1.18</v>
       </c>
       <c r="N13" t="n">
-        <v>45.97</v>
+        <v>45.97000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2547</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2265</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E75" t="n">
+        <v>835</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>336</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-188</v>
+      </c>
+      <c r="J75" t="n">
+        <v>148</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-44</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3887500000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-13.69</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2706603400553578</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.33</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2505079236082893</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
